--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486777_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486777_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8985</v>
+        <v>6.7894</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3422</v>
+        <v>4.556</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5563</v>
+        <v>2.2334</v>
       </c>
       <c r="G2" t="n">
         <v>4.0927</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8057</v>
+        <v>0.6967</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0825</v>
+        <v>0.2963</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7232</v>
+        <v>0.4004</v>
       </c>
       <c r="V2" t="n">
         <v>1.2277</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0865</v>
+        <v>6.3317</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2377</v>
+        <v>5.2915</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8488</v>
+        <v>1.0402</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8093</v>
+        <v>4.4877</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1794</v>
+        <v>1.2346</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6299</v>
+        <v>3.2531</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7275</v>
+        <v>5.2131</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9386</v>
+        <v>1.9939</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7889</v>
+        <v>3.2193</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0818</v>
+        <v>-0.7255</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7591</v>
+        <v>-0.7593</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8409</v>
+        <v>0.0338</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7723</v>
+        <v>0.7723</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1585</v>
+        <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7213</v>
+        <v>0.7861</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.7582</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8941</v>
+        <v>0.0279</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3282</v>
+        <v>0.2856</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6138</v>
+        <v>0.2856</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9812</v>
+        <v>5.5031</v>
       </c>
       <c r="E4" t="n">
-        <v>5.388</v>
+        <v>3.9275</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5931999999999999</v>
+        <v>1.5756</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4877</v>
+        <v>4.8093</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2346</v>
+        <v>0.1794</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2531</v>
+        <v>4.6299</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2131</v>
+        <v>4.7275</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9939</v>
+        <v>0.9386</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2193</v>
+        <v>3.7889</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7255</v>
+        <v>0.0818</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7593</v>
+        <v>-0.7591</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0338</v>
+        <v>0.8409</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7723</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7377</v>
+        <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4356</v>
+        <v>1.1378</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8547</v>
+        <v>0.5169</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.419</v>
+        <v>0.621</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2856</v>
+        <v>0.3282</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2856</v>
+        <v>0.6138</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2719</v>
+        <v>3.5988</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7445</v>
+        <v>1.5929</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5274</v>
+        <v>2.0059</v>
       </c>
       <c r="G5" t="n">
         <v>4.5345</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3559</v>
+        <v>1.6828</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9375</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4184</v>
+        <v>0.8969</v>
       </c>
       <c r="V5" t="n">
         <v>0.8568</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SCHILB</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3588</v>
+        <v>2.6803</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7803</v>
+        <v>2.3979</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5784</v>
+        <v>0.2824</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9520999999999999</v>
+        <v>1.5908</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1036</v>
+        <v>0.2412</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0557</v>
+        <v>1.3496</v>
       </c>
       <c r="J6" t="n">
-        <v>1.753</v>
+        <v>2.0671</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4486</v>
+        <v>0.7242</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3044</v>
+        <v>1.3428</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.4763</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5522</v>
+        <v>-0.483</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2487</v>
+        <v>0.0068</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4067</v>
+        <v>0.5103</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9927</v>
+        <v>0.3309</v>
       </c>
       <c r="U6" t="n">
-        <v>0.414</v>
+        <v>0.1794</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>J. SCHILB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2418</v>
+        <v>2.2761</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9842</v>
+        <v>1.5735</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2575</v>
+        <v>0.7026</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5908</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2412</v>
+        <v>-0.1036</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3496</v>
+        <v>1.0557</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0671</v>
+        <v>1.753</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7242</v>
+        <v>0.4486</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3428</v>
+        <v>1.3044</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4763</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.483</v>
+        <v>-0.5522</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0068</v>
+        <v>-0.2487</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0717</v>
+        <v>1.324</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0828</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1546</v>
+        <v>0.5381</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.146</v>
+        <v>2.0677</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7663</v>
+        <v>0.7379</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3797</v>
+        <v>1.3298</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3314</v>
+        <v>1.1573</v>
       </c>
       <c r="H8" t="n">
-        <v>0.076</v>
+        <v>2.4414</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2554</v>
+        <v>-1.284</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4083</v>
+        <v>2.1449</v>
       </c>
       <c r="K8" t="n">
-        <v>1.042</v>
+        <v>2.7868</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3662</v>
+        <v>-0.6419</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0769</v>
+        <v>-0.9876</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9661</v>
+        <v>-0.3454</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1108</v>
+        <v>-0.6421</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2008</v>
+        <v>0.9104</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2888</v>
+        <v>0.5238</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0881</v>
+        <v>0.3866</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0332</v>
+        <v>1.68</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2188</v>
+        <v>0.7911</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8144</v>
+        <v>0.8888</v>
       </c>
       <c r="G9" t="n">
         <v>0.9557</v>
@@ -1156,13 +1156,13 @@
         <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0774</v>
+        <v>0.7242</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2207</v>
+        <v>0.3516</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2982</v>
+        <v>0.3727</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8817</v>
+        <v>1.1296</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1998</v>
+        <v>1.2547</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0815</v>
+        <v>-0.1251</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1573</v>
+        <v>-0.1603</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4414</v>
+        <v>0.8547</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.284</v>
+        <v>-1.015</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1449</v>
+        <v>1.2477</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7868</v>
+        <v>1.2001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6419</v>
+        <v>0.0476</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9876</v>
+        <v>-1.408</v>
       </c>
       <c r="N10" t="n">
         <v>-0.3454</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6421</v>
+        <v>-1.0626</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2757</v>
+        <v>1.0276</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4139</v>
+        <v>0.7101</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1383</v>
+        <v>0.3175</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1188</v>
+        <v>1.0553</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2687</v>
+        <v>0.477</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1499</v>
+        <v>0.5783</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1603</v>
+        <v>0.3314</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8547</v>
+        <v>0.076</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.015</v>
+        <v>0.2554</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2477</v>
+        <v>1.4083</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2001</v>
+        <v>1.042</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0476</v>
+        <v>0.3662</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.408</v>
+        <v>-1.0769</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3454</v>
+        <v>-0.9661</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0626</v>
+        <v>-0.1108</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9654</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0168</v>
+        <v>1.1101</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2759</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2927</v>
+        <v>0.1106</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7318</v>
+        <v>-1.2489</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9313</v>
+        <v>0.4142</v>
       </c>
       <c r="F12" t="n">
         <v>-1.663</v>
@@ -1390,10 +1390,10 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1307</v>
+        <v>0.6136</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7995</v>
+        <v>0.2824</v>
       </c>
       <c r="U12" t="n">
         <v>0.3312</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.28659999999999</v>
+        <v>31.8631</v>
       </c>
       <c r="E13" t="n">
-        <v>22.4622</v>
+        <v>23.0142</v>
       </c>
       <c r="F13" t="n">
-        <v>8.824300000000001</v>
+        <v>8.8489</v>
       </c>
       <c r="G13" t="n">
         <v>22.4133</v>
@@ -1456,7 +1456,7 @@
         <v>-5.5227</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9367</v>
+        <v>-0.9366999999999998</v>
       </c>
       <c r="P13" t="n">
         <v>-1.9309</v>
@@ -1468,13 +1468,13 @@
         <v>14.4808</v>
       </c>
       <c r="S13" t="n">
-        <v>9.946899999999999</v>
+        <v>10.5236</v>
       </c>
       <c r="T13" t="n">
-        <v>5.7895</v>
+        <v>6.3413</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1576</v>
+        <v>4.1823</v>
       </c>
       <c r="V13" t="n">
         <v>0.8568000000000002</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6184</v>
+        <v>1.6257</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4996</v>
+        <v>4.0471</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.8812</v>
+        <v>-2.4214</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2832</v>
+        <v>0.3428</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3657</v>
+        <v>-0.1726</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6489</v>
+        <v>0.5155</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3871</v>
+        <v>2.4402</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5733</v>
+        <v>0.7242</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8138</v>
+        <v>1.7159</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.6703</v>
+        <v>-2.0973</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2076</v>
+        <v>-0.8969</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4627</v>
+        <v>-1.2005</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07140000000000001</v>
+        <v>-0.9102</v>
       </c>
       <c r="T14" t="n">
-        <v>1.02</v>
+        <v>-0.2346</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9486</v>
+        <v>-0.6756</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2856</v>
+        <v>1.8415</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3058</v>
+        <v>0.9952</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8402</v>
+        <v>3.4654</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5344</v>
+        <v>-2.4702</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3428</v>
+        <v>-0.2832</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1726</v>
+        <v>0.3657</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5155</v>
+        <v>-0.6489</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4402</v>
+        <v>3.3871</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7242</v>
+        <v>2.5733</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7159</v>
+        <v>0.8138</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0973</v>
+        <v>-3.6703</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8969</v>
+        <v>-2.2076</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2005</v>
+        <v>-1.4627</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2301</v>
+        <v>-0.5518</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4415</v>
+        <v>-0.0142</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7886</v>
+        <v>-0.5376</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8415</v>
+        <v>0.2856</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9821</v>
+        <v>-0.8331</v>
       </c>
       <c r="E16" t="n">
         <v>2.1488</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1309</v>
+        <v>-2.9819</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0242</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2249</v>
+        <v>-1.0759</v>
       </c>
       <c r="T16" t="n">
         <v>-0.4142</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8108</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-1.4707</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4659</v>
+        <v>-1.2549</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3779</v>
+        <v>-0.0677</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.088</v>
+        <v>-1.1873</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1309</v>
@@ -1780,13 +1780,13 @@
         <v>2.3169</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7211</v>
+        <v>-1.5102</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1588</v>
+        <v>-0.8486</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5623</v>
+        <v>-0.6616</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.0389</v>
+        <v>-3.3632</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3896</v>
+        <v>0.8033</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4285</v>
+        <v>-4.1664</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1838</v>
@@ -1858,13 +1858,13 @@
         <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8205</v>
+        <v>-1.1447</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7174</v>
+        <v>-0.3037</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1031</v>
+        <v>-0.8411</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2277</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>A. BRASSEUR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.7543</v>
+        <v>-4.8592</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.4526</v>
+        <v>-2.272</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3017</v>
+        <v>-2.5872</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.6398</v>
+        <v>-3.742</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3581</v>
+        <v>-0.3036</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.2816</v>
+        <v>-3.4384</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.7213</v>
+        <v>0.1281</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0471</v>
+        <v>1.4211</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.6742</v>
+        <v>-1.293</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9184</v>
+        <v>-3.8702</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.311</v>
+        <v>-1.7247</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6074</v>
+        <v>-2.1454</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1931</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1239</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9308</v>
+        <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1365</v>
+        <v>-1.3103</v>
       </c>
       <c r="T19" t="n">
-        <v>0.165</v>
+        <v>-0.4693</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9716</v>
+        <v>-0.8409</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BRASSEUR</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8233</v>
+        <v>-5.1331</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.272</v>
+        <v>-3.5667</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5513</v>
+        <v>-1.5664</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.742</v>
+        <v>-2.885</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3036</v>
+        <v>-1.2212</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.4384</v>
+        <v>-1.6638</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1281</v>
+        <v>-0.9805</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4211</v>
+        <v>0.4345</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.293</v>
+        <v>-1.4151</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.8702</v>
+        <v>-1.9044</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7247</v>
+        <v>-1.6557</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1454</v>
+        <v>-0.2487</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-2.1239</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1239</v>
+        <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2744</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4693</v>
+        <v>-0.4623</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.805</v>
+        <v>-0.2066</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6669</v>
+        <v>-5.2643</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8769</v>
+        <v>-4.4563</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7899</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.885</v>
+        <v>-3.0851</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2212</v>
+        <v>-1.7039</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6638</v>
+        <v>-1.3812</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9805</v>
+        <v>-0.5667</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4345</v>
+        <v>0.1589</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4151</v>
+        <v>-0.7256</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9044</v>
+        <v>-2.5184</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6557</v>
+        <v>-1.8628</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2487</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P21" t="n">
         <v>-0.9654</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1239</v>
+        <v>-3.0892</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1585</v>
+        <v>2.1239</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2027</v>
+        <v>-1.2138</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7725</v>
+        <v>-0.8003</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4301</v>
+        <v>-0.4135</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9759</v>
+        <v>-5.9667</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.87</v>
+        <v>-4.9697</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.106</v>
+        <v>-0.997</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0851</v>
+        <v>-6.6398</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7039</v>
+        <v>-2.3581</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3812</v>
+        <v>-4.2816</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5667</v>
+        <v>-3.7213</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1589</v>
+        <v>-1.0471</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7256</v>
+        <v>-2.6742</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5184</v>
+        <v>-2.9184</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8628</v>
+        <v>-1.311</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-1.6074</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.0892</v>
+        <v>-2.1239</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1239</v>
+        <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9254</v>
+        <v>-0.0759</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.214</v>
+        <v>-0.3522</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7114</v>
+        <v>0.2763</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3489</v>
+        <v>-6.389</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6985</v>
+        <v>-3.8019</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6504</v>
+        <v>-2.587</v>
       </c>
       <c r="G23" t="n">
         <v>-4.6443</v>
@@ -2248,13 +2248,13 @@
         <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7393</v>
+        <v>-0.7793</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1383</v>
+        <v>-0.2417</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.601</v>
+        <v>-0.5376</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-31.132</v>
+        <v>-30.4426</v>
       </c>
       <c r="E24" t="n">
         <v>-8.669699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.4623</v>
+        <v>-21.7728</v>
       </c>
       <c r="G24" t="n">
         <v>-22.2755</v>
@@ -2299,7 +2299,7 @@
         <v>-10.8962</v>
       </c>
       <c r="J24" t="n">
-        <v>6.597399999999999</v>
+        <v>6.597400000000001</v>
       </c>
       <c r="K24" t="n">
         <v>5.5227</v>
@@ -2317,7 +2317,7 @@
         <v>-11.9708</v>
       </c>
       <c r="P24" t="n">
-        <v>1.930799999999999</v>
+        <v>1.9308</v>
       </c>
       <c r="Q24" t="n">
         <v>-14.481</v>
@@ -2326,16 +2326,16 @@
         <v>16.4118</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.9305</v>
+        <v>-9.241</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.141</v>
+        <v>-4.1411</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.789300000000001</v>
+        <v>-5.1</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8567999999999998</v>
+        <v>-0.8567999999999997</v>
       </c>
       <c r="W24" t="n">
         <v>3.3548</v>
